--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_3_3.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_3_3.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20640" windowHeight="9765"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表3-3资产负债剩余期限" sheetId="4" r:id="rId1"/>
@@ -16,7 +21,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -47,9 +52,6 @@
     <t>产品品种：</t>
   </si>
   <si>
-    <t>单位：万元</t>
-  </si>
-  <si>
     <t>列编号</t>
   </si>
   <si>
@@ -108,6 +110,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1个月（含）以下</t>
@@ -124,6 +127,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1-3个月（含）</t>
@@ -140,6 +144,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>3-6个月（含）</t>
@@ -156,6 +161,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>6-12个月（含）</t>
@@ -172,6 +178,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1-2年（含）</t>
@@ -188,6 +195,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>2-3年（含）</t>
@@ -204,6 +212,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>3年以上</t>
@@ -220,6 +229,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>无固定期限</t>
@@ -441,6 +451,10 @@
   </si>
   <si>
     <t>${report.prodVariety}</t>
+  </si>
+  <si>
+    <t>单位：万元</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -450,7 +464,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.000000_ "/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -468,12 +482,14 @@
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -490,17 +506,20 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -610,7 +629,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -661,7 +680,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -712,8 +731,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -742,6 +764,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -750,74 +775,10 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="使用说明"/>
       <sheetName val="综合校验"/>
-      <sheetName val="模板校验关系"/>
-      <sheetName val="目录"/>
-      <sheetName val="表1-1募集余额"/>
-      <sheetName val="表1-2募集及兑付发生额"/>
-      <sheetName val="表1-3只数情况"/>
-      <sheetName val="表1-4境内募集余额分地区"/>
-      <sheetName val="表1-5提前及延期兑付"/>
-      <sheetName val="表1-6到期未兑付"/>
-      <sheetName val="表2-1资产负债"/>
-      <sheetName val="表2-2除回购和拆借外贷款按行业、企业"/>
-      <sheetName val="表2-3除回购和拆借外贷款分地区"/>
-      <sheetName val="表2-4资产收益权按基础资产投向"/>
-      <sheetName val="表2-5企业债券按行业、企业"/>
-      <sheetName val="表3-1存续产品分期限募集余额"/>
-      <sheetName val="表3-2新发产品分期限募集金额"/>
-      <sheetName val="表3-3资产负债剩余期限"/>
-      <sheetName val="目录0"/>
-      <sheetName val="表1-1募集余额0"/>
-      <sheetName val="表1-2募集及兑付发生额0"/>
-      <sheetName val="表1-3只数情况0"/>
-      <sheetName val="表1-4境内募集余额分地区0"/>
-      <sheetName val="表1-5提前及延期兑付0"/>
-      <sheetName val="表1-6到期未兑付0"/>
-      <sheetName val="表2-1资产负债0"/>
-      <sheetName val="表2-2除回购和拆借外贷款按行业、企业0"/>
-      <sheetName val="表2-3除回购和拆借外贷款分地区0"/>
-      <sheetName val="表2-4资产收益权按基础资产投向0"/>
-      <sheetName val="表2-5企业债券按行业、企业0"/>
-      <sheetName val="表3-1存续产品分期限募集余额0"/>
-      <sheetName val="表3-2新发产品分期限募集金额0"/>
-      <sheetName val="表3-3资产负债剩余期限0"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1094,15 +1055,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="21" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="A1" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
@@ -1112,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
@@ -1143,310 +1104,310 @@
         <v>7</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="34"/>
       <c r="D4" s="35"/>
       <c r="E4" s="36"/>
       <c r="F4" s="37"/>
-      <c r="G4" s="32" t="s">
-        <v>8</v>
+      <c r="G4" s="40" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="27"/>
       <c r="B5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="E5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="F5" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="G5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="31" t="s">
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="43" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="42" t="s">
+      <c r="B6" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="42" t="s">
+      <c r="G6" s="43"/>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="43"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="42"/>
-    </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="42"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="E8" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="F8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="G8" s="22" t="s">
         <v>52</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="E9" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="F9" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="G9" s="22" t="s">
         <v>57</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="E10" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="F10" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="G10" s="22" t="s">
         <v>62</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="F11" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="G11" s="22" t="s">
         <v>67</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="E12" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="F12" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="G12" s="22" t="s">
         <v>72</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>34</v>
-      </c>
       <c r="C13" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="E13" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="F13" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="G13" s="22" t="s">
         <v>77</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>36</v>
-      </c>
       <c r="C14" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="F14" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="G14" s="22" t="s">
         <v>82</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>38</v>
-      </c>
       <c r="C15" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="E15" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="F15" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="G15" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="C16" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="105" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
     </row>
     <row r="18" spans="1:7" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>43</v>
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="F18" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="G18" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
